--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65809277</v>
+        <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>5207</v>
+        <v>100608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100572</v>
+        <v>178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre ekbock</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cerambyx scopolii</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fuessly, 1775</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
+          <t>(Huds.) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ebbeskogsgatan., Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622596</v>
+        <v>622539</v>
       </c>
       <c r="R2" t="n">
-        <v>6356159</v>
+        <v>6355997</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-08-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,79 +761,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Ekstock.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65809277</t>
+          <t>https://artportalen.se/Sighting/137151976</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2156821</v>
+        <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>111175</v>
+        <v>100922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622629</v>
+        <v>622542</v>
       </c>
       <c r="R3" t="n">
-        <v>6356226</v>
+        <v>6355968</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,83 +863,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>lövskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2156821</t>
+          <t>https://artportalen.se/Sighting/137151998</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2279123</v>
+        <v>137152103</v>
       </c>
       <c r="B4" t="n">
-        <v>99010</v>
+        <v>75566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219769</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lindresrvatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622743</v>
+        <v>622515</v>
       </c>
       <c r="R4" t="n">
-        <v>6356252</v>
+        <v>6355946</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,39 +966,35 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>vägkant</t>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2279123</t>
+          <t>https://artportalen.se/Sighting/137152103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2279124</v>
+        <v>137152126</v>
       </c>
       <c r="B5" t="n">
-        <v>99010</v>
+        <v>78886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,42 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219769</v>
+        <v>6436</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622681</v>
+        <v>622629</v>
       </c>
       <c r="R5" t="n">
-        <v>6356183</v>
+        <v>6355681</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,39 +1073,35 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark, frisk</t>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2279124</t>
+          <t>https://artportalen.se/Sighting/137152126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2279125</v>
+        <v>137152127</v>
       </c>
       <c r="B6" t="n">
-        <v>99010</v>
+        <v>78886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,42 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219769</v>
+        <v>6436</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622625</v>
+        <v>622587</v>
       </c>
       <c r="R6" t="n">
-        <v>6356012</v>
+        <v>6355862</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,12 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,82 +1180,87 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark, frisk</t>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Ek på hygge</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2279125</t>
+          <t>https://artportalen.se/Sighting/137152127</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2311109</v>
+        <v>65809277</v>
       </c>
       <c r="B7" t="n">
-        <v>99142</v>
+        <v>5207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>100572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre ekbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cerambyx scopolii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Fuessly, 1775</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebbeskogsgatan., Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622686</v>
+        <v>622596</v>
       </c>
       <c r="R7" t="n">
-        <v>6356197</v>
+        <v>6356159</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,12 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>1995-08-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>1995-08-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,37 +1308,38 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Ekstock.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2311109</t>
+          <t>https://artportalen.se/Sighting/65809277</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67239083</v>
+        <v>2156821</v>
       </c>
       <c r="B8" t="n">
-        <v>99148</v>
+        <v>111175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,16 +1347,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219865</v>
+        <v>219677</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,14 +1367,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lindreservatet norrut, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622559</v>
+        <v>622629</v>
       </c>
       <c r="R8" t="n">
-        <v>6355595</v>
+        <v>6356226</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,18 +1420,18 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>fårbetad alvarlik mark</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Ingela Carlström, Tommy Carlström, Stephanie Janowski</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1491,16 +1441,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67239083</t>
+          <t>https://artportalen.se/Sighting/2156821</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3572246</v>
+        <v>2279123</v>
       </c>
       <c r="B9" t="n">
-        <v>99138</v>
+        <v>99010</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221119</v>
+        <v>219769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Krutbrännare</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neotinea ustulata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. M. Bateman et al.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,14 +1483,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindresrvatet norr, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622627</v>
+        <v>622743</v>
       </c>
       <c r="R9" t="n">
-        <v>6356033</v>
+        <v>6356252</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1536,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1607,16 +1557,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3572246</t>
+          <t>https://artportalen.se/Sighting/2279123</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3384122</v>
+        <v>2279124</v>
       </c>
       <c r="B10" t="n">
-        <v>106155</v>
+        <v>99010</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,27 +1574,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>219769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1653,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622627</v>
+        <v>622681</v>
       </c>
       <c r="R10" t="n">
-        <v>6356033</v>
+        <v>6356183</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1723,16 +1673,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3384122</t>
+          <t>https://artportalen.se/Sighting/2279124</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3787736</v>
+        <v>2279125</v>
       </c>
       <c r="B11" t="n">
-        <v>106328</v>
+        <v>99010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221423</v>
+        <v>219769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,14 +1715,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lindresrvatet norr, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622743</v>
+        <v>622625</v>
       </c>
       <c r="R11" t="n">
-        <v>6356252</v>
+        <v>6356012</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,7 +1768,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>nyröjd betesmark, frisk</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1839,16 +1789,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787736</t>
+          <t>https://artportalen.se/Sighting/2279125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3787737</v>
+        <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>106328</v>
+        <v>99264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,42 +1806,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221423</v>
+        <v>219769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622681</v>
+        <v>622536</v>
       </c>
       <c r="R12" t="n">
-        <v>6356183</v>
+        <v>6356003</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,12 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,40 +1876,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark, frisk</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787737</t>
+          <t>https://artportalen.se/Sighting/137151943</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3787738</v>
+        <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>106328</v>
+        <v>99350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,42 +1908,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221423</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622598</v>
+        <v>622533</v>
       </c>
       <c r="R13" t="n">
-        <v>6356122</v>
+        <v>6355999</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,75 +1978,71 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>ädellövskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787738</t>
+          <t>https://artportalen.se/Sighting/137152004</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4709118</v>
+        <v>2311109</v>
       </c>
       <c r="B14" t="n">
-        <v>99754</v>
+        <v>99142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222295</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622681</v>
+        <v>622686</v>
       </c>
       <c r="R14" t="n">
-        <v>6356183</v>
+        <v>6356197</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2181,6 +2108,910 @@
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2311109</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>67239083</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219865</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Johannesnycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Orchis militaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lindreservatet norrut, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>622559</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6355595</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-08-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-08-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>fårbetad alvarlik mark</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Ingela Carlström, Tommy Carlström, Stephanie Janowski</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67239083</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3572246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99138</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221119</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Krutbrännare</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neotinea ustulata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. M. Bateman et al.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>622627</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6356033</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3572246</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3384122</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>622627</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6356033</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3384122</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3787736</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lindresrvatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>622743</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6356252</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787736</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3787737</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>622681</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6356183</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787737</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3787738</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>622598</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6356122</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787738</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137152188</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107331</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ebberskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>622604</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6355714</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137152188</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4709118</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>622681</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6356183</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/4709118</t>
         </is>
@@ -2201,6 +3032,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100608</v>
+        <v>100610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100922</v>
+        <v>100924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99264</v>
+        <v>99266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100610</v>
+        <v>100612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100924</v>
+        <v>100926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137152126</v>
       </c>
       <c r="B5" t="n">
-        <v>78886</v>
+        <v>78889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137152127</v>
       </c>
       <c r="B6" t="n">
-        <v>78886</v>
+        <v>78889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99266</v>
+        <v>99268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100612</v>
+        <v>100625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100926</v>
+        <v>100939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137152103</v>
       </c>
       <c r="B4" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137152126</v>
       </c>
       <c r="B5" t="n">
-        <v>78889</v>
+        <v>78902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137152127</v>
       </c>
       <c r="B6" t="n">
-        <v>78889</v>
+        <v>78902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99268</v>
+        <v>99281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107335</v>
+        <v>107348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100625</v>
+        <v>100627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137152103</v>
       </c>
       <c r="B4" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137152126</v>
       </c>
       <c r="B5" t="n">
-        <v>78902</v>
+        <v>78904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137152127</v>
       </c>
       <c r="B6" t="n">
-        <v>78902</v>
+        <v>78904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99281</v>
+        <v>99283</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107348</v>
+        <v>107350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100627</v>
+        <v>100630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100941</v>
+        <v>100944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99283</v>
+        <v>99286</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107350</v>
+        <v>107354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100630</v>
+        <v>100640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100944</v>
+        <v>100954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137152103</v>
       </c>
       <c r="B4" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137152126</v>
       </c>
       <c r="B5" t="n">
-        <v>78904</v>
+        <v>78914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137152127</v>
       </c>
       <c r="B6" t="n">
-        <v>78904</v>
+        <v>78914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99286</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107354</v>
+        <v>107374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100640</v>
+        <v>100641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100954</v>
+        <v>100955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137151943</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137152004</v>
       </c>
       <c r="B13" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137152188</v>
       </c>
       <c r="B21" t="n">
-        <v>107374</v>
+        <v>107375</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,48 +884,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137152103</v>
+        <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>75591</v>
+        <v>100955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>783</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622515</v>
+        <v>622542</v>
       </c>
       <c r="R4" t="n">
-        <v>6355946</v>
+        <v>6355969</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,6 +951,11 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Hö-Bor-3947</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
@@ -954,7 +963,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,60 +972,60 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Ek</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Joakim Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137152103</t>
+          <t>https://artportalen.se/Sighting/137356664</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137152126</v>
+        <v>137152103</v>
       </c>
       <c r="B5" t="n">
-        <v>78914</v>
+        <v>75591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6436</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622629</v>
+        <v>622515</v>
       </c>
       <c r="R5" t="n">
-        <v>6355681</v>
+        <v>6355946</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,13 +1101,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137152126</t>
+          <t>https://artportalen.se/Sighting/137152103</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137152127</v>
+        <v>137152126</v>
       </c>
       <c r="B6" t="n">
         <v>78914</v>
@@ -1133,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622587</v>
+        <v>622629</v>
       </c>
       <c r="R6" t="n">
-        <v>6355862</v>
+        <v>6355681</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1191,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Ek på hygge</t>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1199,65 +1208,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137152127</t>
+          <t>https://artportalen.se/Sighting/137152126</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65809277</v>
+        <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>5207</v>
+        <v>78914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100572</v>
+        <v>6436</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre ekbock</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cerambyx scopolii</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fuessly, 1775</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ebbeskogsgatan., Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622596</v>
+        <v>622587</v>
       </c>
       <c r="R7" t="n">
-        <v>6356159</v>
+        <v>6355862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,17 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1995-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1995-08-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,78 +1296,87 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Ekstock.</t>
+          <t>Ek på hygge</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65809277</t>
+          <t>https://artportalen.se/Sighting/137152127</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2156821</v>
+        <v>65809277</v>
       </c>
       <c r="B8" t="n">
-        <v>111175</v>
+        <v>5207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219677</v>
+        <v>100572</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Mindre ekbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cerambyx scopolii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Fuessly, 1775</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebbeskogsgatan., Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622629</v>
+        <v>622596</v>
       </c>
       <c r="R8" t="n">
-        <v>6356226</v>
+        <v>6356159</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,12 +1400,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>1995-08-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>1995-08-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,37 +1424,38 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Ekstock.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2156821</t>
+          <t>https://artportalen.se/Sighting/65809277</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2279123</v>
+        <v>2156821</v>
       </c>
       <c r="B9" t="n">
-        <v>99010</v>
+        <v>111175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,39 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219769</v>
+        <v>219677</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lindresrvatet norr, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622743</v>
+        <v>622629</v>
       </c>
       <c r="R9" t="n">
-        <v>6356252</v>
+        <v>6356226</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1557,13 +1557,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2279123</t>
+          <t>https://artportalen.se/Sighting/2156821</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2279124</v>
+        <v>2279123</v>
       </c>
       <c r="B10" t="n">
         <v>99010</v>
@@ -1599,14 +1599,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindresrvatet norr, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622681</v>
+        <v>622743</v>
       </c>
       <c r="R10" t="n">
-        <v>6356183</v>
+        <v>6356252</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2279124</t>
+          <t>https://artportalen.se/Sighting/2279123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2279125</v>
+        <v>2279124</v>
       </c>
       <c r="B11" t="n">
         <v>99010</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622625</v>
+        <v>622681</v>
       </c>
       <c r="R11" t="n">
-        <v>6356012</v>
+        <v>6356183</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,16 +1789,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2279125</t>
+          <t>https://artportalen.se/Sighting/2279124</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137151943</v>
+        <v>2279125</v>
       </c>
       <c r="B12" t="n">
-        <v>99297</v>
+        <v>99010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,19 +1824,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ebberskog, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622536</v>
+        <v>622625</v>
       </c>
       <c r="R12" t="n">
-        <v>6356003</v>
+        <v>6356012</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,12 +1865,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,31 +1881,40 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137151943</t>
+          <t>https://artportalen.se/Sighting/2279125</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137152004</v>
+        <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99383</v>
+        <v>99297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,21 +1922,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622533</v>
+        <v>622536</v>
       </c>
       <c r="R13" t="n">
-        <v>6355999</v>
+        <v>6356003</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,16 +2007,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137152004</t>
+          <t>https://artportalen.se/Sighting/137151943</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2311109</v>
+        <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99142</v>
+        <v>99383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2010,42 +2024,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622686</v>
+        <v>622533</v>
       </c>
       <c r="R14" t="n">
-        <v>6356197</v>
+        <v>6355999</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2069,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,40 +2094,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark, frisk</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2311109</t>
+          <t>https://artportalen.se/Sighting/137152004</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67239083</v>
+        <v>2311109</v>
       </c>
       <c r="B15" t="n">
-        <v>99148</v>
+        <v>99142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,34 +2126,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219865</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lindreservatet norrut, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622559</v>
+        <v>622686</v>
       </c>
       <c r="R15" t="n">
-        <v>6355595</v>
+        <v>6356197</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2180,12 +2185,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,18 +2204,18 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>fårbetad alvarlik mark</t>
+          <t>nyröjd betesmark, frisk</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Ingela Carlström, Tommy Carlström, Stephanie Janowski</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2220,16 +2225,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67239083</t>
+          <t>https://artportalen.se/Sighting/2311109</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3572246</v>
+        <v>67239083</v>
       </c>
       <c r="B16" t="n">
-        <v>99138</v>
+        <v>99148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,39 +2242,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221119</v>
+        <v>219865</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Krutbrännare</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neotinea ustulata</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. M. Bateman et al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindreservatet norrut, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622627</v>
+        <v>622559</v>
       </c>
       <c r="R16" t="n">
-        <v>6356033</v>
+        <v>6355595</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,18 +2315,18 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>fårbetad alvarlik mark</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Ingela Carlström, Tommy Carlström, Stephanie Janowski</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2336,16 +2336,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3572246</t>
+          <t>https://artportalen.se/Sighting/67239083</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3384122</v>
+        <v>3572246</v>
       </c>
       <c r="B17" t="n">
-        <v>106155</v>
+        <v>99138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,27 +2353,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>221119</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Krutbrännare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neotinea ustulata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. M. Bateman et al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2452,16 +2452,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3384122</t>
+          <t>https://artportalen.se/Sighting/3572246</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3787736</v>
+        <v>3384122</v>
       </c>
       <c r="B18" t="n">
-        <v>106328</v>
+        <v>106155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,39 +2469,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221423</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lindresrvatet norr, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622743</v>
+        <v>622627</v>
       </c>
       <c r="R18" t="n">
-        <v>6356252</v>
+        <v>6356033</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>nyröjd betesmark, frisk</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2568,13 +2568,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787736</t>
+          <t>https://artportalen.se/Sighting/3384122</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3787737</v>
+        <v>3787736</v>
       </c>
       <c r="B19" t="n">
         <v>106328</v>
@@ -2610,14 +2610,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindresrvatet norr, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622681</v>
+        <v>622743</v>
       </c>
       <c r="R19" t="n">
-        <v>6356183</v>
+        <v>6356252</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2684,13 +2684,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787737</t>
+          <t>https://artportalen.se/Sighting/3787736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3787738</v>
+        <v>3787737</v>
       </c>
       <c r="B20" t="n">
         <v>106328</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622598</v>
+        <v>622681</v>
       </c>
       <c r="R20" t="n">
-        <v>6356122</v>
+        <v>6356183</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>ädellövskog</t>
+          <t>nyröjd betesmark, frisk</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2800,54 +2800,59 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3787738</t>
+          <t>https://artportalen.se/Sighting/3787737</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137152188</v>
+        <v>3787738</v>
       </c>
       <c r="B21" t="n">
-        <v>107375</v>
+        <v>106328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221903</v>
+        <v>221423</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ebberskog, Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622604</v>
+        <v>622598</v>
       </c>
       <c r="R21" t="n">
-        <v>6355714</v>
+        <v>6356122</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,12 +2876,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,31 +2892,40 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137152188</t>
+          <t>https://artportalen.se/Sighting/3787738</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4709118</v>
+        <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>99754</v>
+        <v>107375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,37 +2933,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222295</v>
+        <v>221903</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622681</v>
+        <v>622604</v>
       </c>
       <c r="R22" t="n">
-        <v>6356183</v>
+        <v>6355714</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,12 +2987,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,29 +3003,131 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark, frisk</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137152188</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4709118</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>622681</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6356183</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/4709118</t>
         </is>
@@ -3040,6 +3156,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100641</v>
+        <v>100646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100955</v>
+        <v>100960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100955</v>
+        <v>100960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137152103</v>
       </c>
       <c r="B5" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137152126</v>
       </c>
       <c r="B6" t="n">
-        <v>78914</v>
+        <v>78917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>78914</v>
+        <v>78917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99297</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107375</v>
+        <v>107380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100646</v>
+        <v>100649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100960</v>
+        <v>100963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100960</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107380</v>
+        <v>107383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100649</v>
+        <v>100655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>100969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137152103</v>
       </c>
       <c r="B5" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137152126</v>
       </c>
       <c r="B6" t="n">
-        <v>78917</v>
+        <v>78922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>78917</v>
+        <v>78922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99304</v>
+        <v>99310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107383</v>
+        <v>107389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107389</v>
+        <v>107390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100655</v>
+        <v>100667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100969</v>
+        <v>100981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>100981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137152103</v>
       </c>
       <c r="B5" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137152126</v>
       </c>
       <c r="B6" t="n">
-        <v>78922</v>
+        <v>78933</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>78922</v>
+        <v>78933</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99310</v>
+        <v>99322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107390</v>
+        <v>107402</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100667</v>
+        <v>100668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100981</v>
+        <v>100982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100981</v>
+        <v>100982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137152126</v>
       </c>
       <c r="B6" t="n">
-        <v>78933</v>
+        <v>78934</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>78933</v>
+        <v>78934</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107402</v>
+        <v>107403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100668</v>
+        <v>100671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100982</v>
+        <v>100985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100982</v>
+        <v>100985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137152126</v>
       </c>
       <c r="B6" t="n">
-        <v>78934</v>
+        <v>78936</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>78934</v>
+        <v>78936</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99323</v>
+        <v>99326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107403</v>
+        <v>107406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100671</v>
+        <v>100675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100985</v>
+        <v>100989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100985</v>
+        <v>100989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137152103</v>
       </c>
       <c r="B5" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>137152126</v>
       </c>
       <c r="B6" t="n">
-        <v>78936</v>
+        <v>78940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137152127</v>
       </c>
       <c r="B7" t="n">
-        <v>78936</v>
+        <v>78940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99326</v>
+        <v>99330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107406</v>
+        <v>107412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137151976</v>
       </c>
       <c r="B2" t="n">
-        <v>100675</v>
+        <v>100677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151998</v>
       </c>
       <c r="B3" t="n">
-        <v>100989</v>
+        <v>100991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137356664</v>
       </c>
       <c r="B4" t="n">
-        <v>100989</v>
+        <v>100991</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>137151943</v>
       </c>
       <c r="B13" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137152004</v>
       </c>
       <c r="B14" t="n">
-        <v>99416</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137152188</v>
       </c>
       <c r="B22" t="n">
-        <v>107412</v>
+        <v>107414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
